--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-09-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF8C82C-3345-4359-8ED9-210025DA223D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBAB457-C26D-4019-9ADD-0FD763E9C835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="480" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33750" yWindow="1410" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="397">
   <si>
     <t>SKU</t>
   </si>
@@ -1135,54 +1135,9 @@
     <t>£2756.16</t>
   </si>
   <si>
-    <t>£14.33</t>
-  </si>
-  <si>
-    <t>£16.82</t>
-  </si>
-  <si>
-    <t>£21.37</t>
-  </si>
-  <si>
-    <t>£22.20</t>
-  </si>
-  <si>
-    <t>£26.84</t>
-  </si>
-  <si>
-    <t>£30.80</t>
-  </si>
-  <si>
     <t>£30.13</t>
   </si>
   <si>
-    <t>£33.87</t>
-  </si>
-  <si>
-    <t>£37.75</t>
-  </si>
-  <si>
-    <t>£37.64</t>
-  </si>
-  <si>
-    <t>£47.43</t>
-  </si>
-  <si>
-    <t>£62.22</t>
-  </si>
-  <si>
-    <t>£58.72</t>
-  </si>
-  <si>
-    <t>£56.81</t>
-  </si>
-  <si>
-    <t>£1086.48</t>
-  </si>
-  <si>
-    <t>£1484.74</t>
-  </si>
-  <si>
     <t>£41.49</t>
   </si>
   <si>
@@ -1208,6 +1163,54 @@
   </si>
   <si>
     <t>£2207.68</t>
+  </si>
+  <si>
+    <t>£14.03</t>
+  </si>
+  <si>
+    <t>£16.68</t>
+  </si>
+  <si>
+    <t>£20.90</t>
+  </si>
+  <si>
+    <t>£21.72</t>
+  </si>
+  <si>
+    <t>£26.28</t>
+  </si>
+  <si>
+    <t>£29.46</t>
+  </si>
+  <si>
+    <t>£33.13</t>
+  </si>
+  <si>
+    <t>£36.93</t>
+  </si>
+  <si>
+    <t>£36.82</t>
+  </si>
+  <si>
+    <t>£46.97</t>
+  </si>
+  <si>
+    <t>£46.38</t>
+  </si>
+  <si>
+    <t>£60.85</t>
+  </si>
+  <si>
+    <t>£57.43</t>
+  </si>
+  <si>
+    <t>£55.56</t>
+  </si>
+  <si>
+    <t>£1062.59</t>
+  </si>
+  <si>
+    <t>£1452.11</t>
   </si>
 </sst>
 </file>
@@ -1735,7 +1738,7 @@
         <v>30</v>
       </c>
       <c r="Q3" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="R3" t="s">
         <v>37</v>
@@ -1791,7 +1794,7 @@
         <v>48</v>
       </c>
       <c r="Q4" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="R4" t="s">
         <v>49</v>
@@ -1847,7 +1850,7 @@
         <v>52</v>
       </c>
       <c r="Q5" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="R5" t="s">
         <v>59</v>
@@ -1903,7 +1906,7 @@
         <v>70</v>
       </c>
       <c r="Q6" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="R6" t="s">
         <v>71</v>
@@ -1959,7 +1962,7 @@
         <v>81</v>
       </c>
       <c r="Q7" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="R7" t="s">
         <v>82</v>
@@ -2015,7 +2018,7 @@
         <v>85</v>
       </c>
       <c r="Q8" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="R8" t="s">
         <v>93</v>
@@ -2071,7 +2074,7 @@
         <v>96</v>
       </c>
       <c r="Q9" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="R9" t="s">
         <v>103</v>
@@ -2127,7 +2130,7 @@
         <v>113</v>
       </c>
       <c r="Q10" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="R10" t="s">
         <v>114</v>
@@ -2183,7 +2186,7 @@
         <v>124</v>
       </c>
       <c r="Q11" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="R11" t="s">
         <v>125</v>
@@ -2239,7 +2242,7 @@
         <v>136</v>
       </c>
       <c r="Q12" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="R12" t="s">
         <v>137</v>
@@ -2295,7 +2298,7 @@
         <v>146</v>
       </c>
       <c r="Q13" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="R13" t="s">
         <v>147</v>
@@ -2351,7 +2354,7 @@
         <v>158</v>
       </c>
       <c r="Q14" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="R14" t="s">
         <v>159</v>
@@ -2407,7 +2410,7 @@
         <v>162</v>
       </c>
       <c r="Q15" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="R15" t="s">
         <v>170</v>
@@ -2463,7 +2466,7 @@
         <v>173</v>
       </c>
       <c r="Q16" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="R16" t="s">
         <v>21</v>
@@ -2519,7 +2522,7 @@
         <v>190</v>
       </c>
       <c r="Q17" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="R17" t="s">
         <v>191</v>
@@ -2575,7 +2578,7 @@
         <v>194</v>
       </c>
       <c r="Q18" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="R18" t="s">
         <v>21</v>
@@ -2631,7 +2634,7 @@
         <v>208</v>
       </c>
       <c r="Q19" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="R19" t="s">
         <v>209</v>
@@ -2687,7 +2690,7 @@
         <v>212</v>
       </c>
       <c r="Q20" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="R20" t="s">
         <v>220</v>
@@ -2743,7 +2746,7 @@
         <v>223</v>
       </c>
       <c r="Q21" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="R21" t="s">
         <v>228</v>
@@ -2799,7 +2802,7 @@
         <v>238</v>
       </c>
       <c r="Q22" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="R22" t="s">
         <v>239</v>
@@ -2855,7 +2858,7 @@
         <v>242</v>
       </c>
       <c r="Q23" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="R23" t="s">
         <v>249</v>
@@ -2911,7 +2914,7 @@
         <v>257</v>
       </c>
       <c r="Q24" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="R24" t="s">
         <v>258</v>
@@ -2967,7 +2970,7 @@
         <v>261</v>
       </c>
       <c r="Q25" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="R25" t="s">
         <v>265</v>
@@ -3079,7 +3082,7 @@
         <v>272</v>
       </c>
       <c r="Q27" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="R27" t="s">
         <v>277</v>
@@ -3135,7 +3138,7 @@
         <v>285</v>
       </c>
       <c r="Q28" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="R28" t="s">
         <v>286</v>
@@ -3191,7 +3194,7 @@
         <v>294</v>
       </c>
       <c r="Q29" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="R29" t="s">
         <v>295</v>
